--- a/config/vip_desc.xlsx
+++ b/config/vip_desc.xlsx
@@ -2002,37 +2002,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#0#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#0#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>V0 Free Privilege Pack: #C0xea7004#</t>
+          <t>V0免费特权包：#C0xea7004#</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Buy Stamina #C0xea7004#3#C0x473E37# times daily</t>
+          <t>每日可购买#C0xea7004#3#C0x473E37#次耐力</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#5#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#5#C0x473E37#次</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Daily Hard Mode Resets: #C0xea7004#1#C0x473E37#</t>
+          <t>硬模式关卡每天可重置#C0xea7004#1#C0x473E37#次</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#10#C0x473E37# times</t>
+          <t>可购买伙伴所持配额容量#C0xea7004#10#C0x473E37#次</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#10#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#10#C0x473E37#次</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -2205,37 +2205,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#60#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#60#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>V1 Privilege Pack: #C0xea7004#Breakthrough Pack</t>
+          <t>V1特权包：#C0xea7004#突破包</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Buy Stamina #C0xea7004#4#C0x473E37# times daily</t>
+          <t>每日可购买耐力#C0xea7004#4#C0x473E37#次</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#10#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#10#C0x473E37#次</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Daily Hard Mode Resets: #C0xea7004#1#C0x473E37#</t>
+          <t>硬模式关卡每天可重置#C0xea7004#1#C0x473E37#次</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#15#C0x473E37# times</t>
+          <t>可购买伙伴所持配额容量#C0xea7004#15#C0x473E37#次</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#15#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#15#C0x473E37#次</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -2408,42 +2408,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#300#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#300#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>V2 Privilege Pack: #C0xea7004#Growth Support Pack</t>
+          <t>V2特权包：#C0xea7004#成长支援包</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Buy Stamina #C0xea7004#5#C0x473E37# times daily</t>
+          <t>每日可购买#C0xea7004#5#C0x473E37#次体力</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#15#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#15#C0x473E37#次</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Daily Hard Mode Resets: #C0xea7004#2#C0x473E37#</t>
+          <t>硬模式关卡每天可重置#C0xea7004#2#C0x473E37#次</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#20#C0x473E37# times</t>
+          <t>可购买伙伴所持配额容量#C0xea7004#20#C0x473E37#次</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#20#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#20#C0x473E37#次</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Includes all V1 perks</t>
+          <t>V1包含所有内容</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -2632,47 +2632,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#600#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#600#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>V3 Privilege Pack: #C0xea7004#Rank S Ally Choice Box</t>
+          <t>V3特权包：#C0xea7004#S等级伙伴选定箱</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>#C0xea7004#Skill Pts recovers every 60s</t>
+          <t>#C0xea7004#技能Pt每60秒回复1pt</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Buy Stamina #C0xea7004#6#C0x473E37# times daily</t>
+          <t>每日可购买耐力#C0xea7004#6#C0x473E37#次</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#20#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#20#C0x473E37#次</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Daily Hard Mode Resets: #C0xea7004#2#C0x473E37#</t>
+          <t>硬模式关卡每天可重置#C0xea7004#2#C0x473E37#次</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#25#C0x473E37# times</t>
+          <t>可购买伙伴所持配额容量#C0xea7004#25#C0x473E37#次</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#25#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#25#C0x473E37#次</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Includes all V2 and below perks</t>
+          <t>包含V2以下的所有特权内容</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -2878,47 +2878,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#1000#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#1000#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>V4 Privilege Pack: #C0xea7004#Rank S Ally Choice Box</t>
+          <t>V4特权包：#C0xea7004#S等级伙伴选定箱</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>#C0xea7004#Unlock 50x Story Sweep</t>
+          <t>#C0xea7004#解放故事模式的50次扫荡</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Buy Stamina #C0xea7004#7#C0x473E37# times daily</t>
+          <t>每日可购买#C0xea7004#7#C0x473E37#次体力</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#25#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#25#C0x473E37#次</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Daily Hard Mode Resets: #C0xea7004#2#C0x473E37#</t>
+          <t>硬模式关卡每天可重置#C0xea7004#2#C0x473E37#次</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#30#C0x473E37# times</t>
+          <t>可购买伙伴所持配额容量#C0xea7004#30#C0x473E37#次</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#30#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#30#C0x473E37#次</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Includes all V3 and below perks</t>
+          <t>V3包含以下所有特权内容</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -3123,57 +3123,57 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#2000#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#2000#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>V5 Privilege Pack: #C0xea7004#Awakening Item</t>
+          <t>V5特权包：#C0xea7004#觉醒道具</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>#C0xea7004#Arena Loss Pts +2</t>
+          <t>#C0xea7004#竞技场的败北Pt+2</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>#C0xea7004#Unlock Supreme Guild Donation</t>
+          <t>#C0xea7004#公会的至尊捐赠解放</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>#C0xea7004#Unlock Daily Mission: Spend Diamonds</t>
+          <t>#C0xea7004#日常任务：解锁“钻石消费”</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>#C0xea7004#Skip Arena battles (no CD)</t>
+          <t>#C0xea7004#竞技场战斗跳过没有冷却时间</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Buy Stamina #C0xea7004#8#C0x473E37# times daily</t>
+          <t>每天可购买#C0xea7004#8#C0x473E37#次体力</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#30#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#30#C0x473E37#次</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Daily Hard Mode Resets: #C0xea7004#3#C0x473E37#</t>
+          <t>硬模式关卡每天可重置#C0xea7004#3#C0x473E37#次</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#35#C0x473E37# times</t>
+          <t>可购买伙伴所持配额容量#C0xea7004#35#C0x473E37#次</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#35#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#35#C0x473E37#次</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -3415,47 +3415,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#3000#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#3000#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>V6 Privilege Pack: #C0xea7004#Rank S Ally Choice Box</t>
+          <t>V6特权包：#C0xea7004#S等级伙伴选定箱</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Buy Stamina #C0xea7004#9#C0x473E37# times daily</t>
+          <t>每日可购买耐力#C0xea7004#9#C0x473E37#次</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>#C0xea7004#Spacetime Battle Pts +10%</t>
+          <t>#C0xea7004#时空激战Pt+10%</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#35#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#35#C0x473E37#次</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Daily Hard Mode Resets: #C0xea7004#3#C0x473E37#</t>
+          <t>硬模式关卡每天可重置#C0xea7004#3#C0x473E37#次</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#40#C0x473E37# times</t>
+          <t>可购买伙伴所持配额容量#C0xea7004#40#C0x473E37#次</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#40#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#40#C0x473E37#次</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Includes all V5 and below perks</t>
+          <t>包含V5以下的全部特权内容</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -3660,47 +3660,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#5000#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#5000#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>V7 Privilege Pack: #C0xea7004#May (Angel) + Avatar</t>
+          <t>V7特权包：#C0xea7004#“梅-天使”+头像</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>#C0xea7004#Unlock Daily Mission: Omni-Shards</t>
+          <t>#C0xea7004#日常任务：解放“万能碎片”</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Buy Stamina #C0xea7004#10#C0x473E37# times daily</t>
+          <t>每日可购买#C0xea7004#10#C0x473E37#次体力</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#40#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#40#C0x473E37#次</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Daily Hard Mode Resets: #C0xea7004#3#C0x473E37#</t>
+          <t>硬模式关卡每天可重置#C0xea7004#3#C0x473E37#次</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#45#C0x473E37# times</t>
+          <t>可购买伙伴所持配额容量#C0xea7004#45#C0x473E37#次</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#45#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#45#C0x473E37#次</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Includes all V6 and below perks</t>
+          <t>包含V6以下的所有特权内容</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -3905,52 +3905,52 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#7000#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#7000#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>V8 Privilege Pack: #C0xea7004#May Decoration + Awakening Item</t>
+          <t>V8特权包：#C0xea7004#角色“鸣”装饰+觉醒道具</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>#C0xea7004#Unlock Daily Mission: Gold Keys</t>
+          <t>#C0xea7004#日常任务：解锁“金钥匙”</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Buy Stamina #C0xea7004#11#C0x473E37# times daily</t>
+          <t>每日可购买耐力#C0xea7004#11#C0x473E37#次</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#45#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#45#C0x473E37#次</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Daily Hard Mode Resets: #C0xea7004#3#C0x473E37#</t>
+          <t>硬模式关卡每天可重置#C0xea7004#3#C0x473E37#次</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#50#C0x473E37# times</t>
+          <t>可购买伙伴所持配额容量#C0xea7004#50#C0x473E37#次</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#50#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#50#C0x473E37#次</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Arena challenge cooldown reduced to 1 min</t>
+          <t>竞技场挑战冷却时间缩短至1分钟</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Includes all V7 and below perks</t>
+          <t>V7包含以下所有特权内容</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -4171,47 +4171,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#10000#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#10000#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>V9 Privilege Pack: #C0xea7004#May Shards + Purple Probe Set</t>
+          <t>V9特权包：#C0xea7004#角色“鸣”的碎片+紫色·探测器套装</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>#C0xea7004#Skill Pts recovers every 5s</t>
+          <t>#C0xea7004#技能Pt每5秒回复1pt</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Buy Stamina #C0xea7004#12#C0x473E37# times daily</t>
+          <t>每天可购买#C0xea7004#12#C0x473E37#次体力</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#50#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#50#C0x473E37#次</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Daily Hard Mode Resets: #C0xea7004#3#C0x473E37#</t>
+          <t>硬模式关卡每天可重置#C0xea7004#3#C0x473E37#次</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#55#C0x473E37# times</t>
+          <t>可购买伙伴所持配额容量#C0xea7004#55#C0x473E37#次</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#55#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#55#C0x473E37#次</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Includes all V8 and below perks</t>
+          <t>V8包含以下所有特权内容</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -4416,52 +4416,52 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#15000#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#15000#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>V10 Privilege Pack: #C0xea7004#May Decoration + Awakening + Purple Item</t>
+          <t>V10特权包：#C0xea7004#角色“咪咪”的装饰+觉醒道具+紫色道具</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>#C0xea7004#Unlock Daily Mission: Talent Rewards</t>
+          <t>#C0xea7004#日常任务：解锁“天赋奖励”</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Buy Stamina #C0xea7004#12#C0x473E37# times daily</t>
+          <t>每天可购买#C0xea7004#12#C0x473E37#次体力</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Daily Path of Trials resets: #C0xea7004#2#C0x473E37#</t>
+          <t>每日试炼之道#C0xea7004#2#C0x473E37#可重置</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#60#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#60#C0x473E37#次</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Daily Hard Mode Resets: #C0xea7004#4#C0x473E37#</t>
+          <t>硬模式关卡每天可重置#C0xea7004#4#C0x473E37#次</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#60#C0x473E37# times</t>
+          <t>可购买伙伴所持配额容量#C0xea7004#60#C0x473E37#次</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#60#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#60#C0x473E37#次</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Includes all V9 and below perks</t>
+          <t>包含V9以下的所有特权内容</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -4682,52 +4682,52 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#20000#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#20000#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>V11 Privilege Pack: #C0xea7004#May Shards + Avatar</t>
+          <t>V11特权包：#C0xea7004#角色“鸣”的碎片+头像</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>#C0xea7004#Unlock Daily Mission: Rune Cores</t>
+          <t>#C0xea7004#日常任务：解放“符文核心”</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>#C0xea7004#Max Dispatch Missions +5</t>
+          <t>#C0xea7004#派遣任务的次数+5</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Buy Stamina #C0xea7004#13#C0x473E37# times daily</t>
+          <t>每日可购买耐力#C0xea7004#13#C0x473E37#次</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#70#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#70#C0x473E37#次</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Daily Hard Mode Resets: #C0xea7004#4#C0x473E37#</t>
+          <t>硬模式关卡每天可重置#C0xea7004#4#C0x473E37#次</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#65#C0x473E37# times</t>
+          <t>可购买伙伴所持配额容量#C0xea7004#65#C0x473E37#次</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#65#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#65#C0x473E37#次</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Includes all V10 and below perks</t>
+          <t>包含V10以下的所有特权内容</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -4936,42 +4936,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#30000#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#30000#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>#C0xea7004#Spacetime Battle Pts +15%</t>
+          <t>#C0xea7004#时空激战Pt+15%</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Buy Stamina #C0xea7004#13#C0x473E37# times daily</t>
+          <t>每日可购买耐力#C0xea7004#13#C0x473E37#次</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#80#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#80#C0x473E37#次</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Daily Hard Mode Resets: #C0xea7004#4#C0x473E37#</t>
+          <t>硬模式关卡每天可重置#C0xea7004#4#C0x473E37#次</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#70#C0x473E37# times</t>
+          <t>伙伴所持有的配额容量可购买#C0xea7004#70#C0x473E37#次</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#70#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#70#C0x473E37#次</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Includes all V11 and below perks</t>
+          <t>V11包含以下所有特权内容</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -5176,52 +5176,52 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#60000#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#60000#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>V13 Privilege Pack: #C0xea7004#Awakening Item</t>
+          <t>V13特权包：#C0xea7004#觉醒道具</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>#C0xea7004#Unlock Daily Mission: Omni-Shard S</t>
+          <t>#C0xea7004#日常任务：解放“万能碎片S”</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>#C0xea7004#No Arena challenge cooldown</t>
+          <t>#C0xea7004#竞技场的挑战冷却时间消失</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Buy Stamina #C0xea7004#14#C0x473E37# times daily</t>
+          <t>每日可购买耐力#C0xea7004#14#C0x473E37#次</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#100#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#100#C0x473E37#次</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Daily Hard Mode Resets: #C0xea7004#5#C0x473E37#</t>
+          <t>硬模式关卡每天可重置#C0xea7004#5#C0x473E37#次</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#80#C0x473E37# times</t>
+          <t>可购买伙伴所持配额容量#C0xea7004#80#C0x473E37#次</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#80#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#80#C0x473E37#次</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Includes all V12 and below perks</t>
+          <t>包含V12以下的所有特权内容</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
@@ -5442,52 +5442,52 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#120000#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#120000#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>V14 Privilege Pack: #C0xea7004#Orange Probe Set x1</t>
+          <t>V14特权包：#C0xea7004#橙·探测器套装×1</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>#C0xea7004#Unlock Daily Mission: Summon Coins</t>
+          <t>#C0xea7004#日常任务：解放“扭蛋硬币”</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>#C0xea7004#Spacetime Battle Pts +30%</t>
+          <t>#C0xea7004#时空激战Pt+30%</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Buy Stamina #C0xea7004#14#C0x473E37# times daily</t>
+          <t>每日可购买耐力#C0xea7004#14#C0x473E37#次</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#120#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#120#C0x473E37#次</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Daily Hard Mode Resets: #C0xea7004#5#C0x473E37#</t>
+          <t>硬模式关卡每天可重置#C0xea7004#5#C0x473E37#次</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#90#C0x473E37# times</t>
+          <t>伙伴所持有的配额容量可购买#C0xea7004#90#C0x473E37#次</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#90#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#90#C0x473E37#次</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Includes all V13 and below perks</t>
+          <t>V13包含以下所有特权内容</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
@@ -5696,42 +5696,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#200000#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#200000#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>V15 Privilege Pack: #C0xea7004#Omni-Shard S + Orange Gear</t>
+          <t>V15特权包：#C0xea7004#万能碎片S+橙·装备</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Buy Stamina #C0xea7004#15#C0x473E37# times daily</t>
+          <t>每日可购买#C0xea7004#15#C0x473E37#次体力</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#150#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#150#C0x473E37#次</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Daily Hard Mode Resets: #C0xea7004#5#C0x473E37#</t>
+          <t>硬模式关卡每天可重置#C0xea7004#5#C0x473E37#次</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#100#C0x473E37# times</t>
+          <t>可购买伙伴所持配额容量#C0xea7004#100#C0x473E37#次</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#100#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#100#C0x473E37#次</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Includes all V14 and below perks</t>
+          <t>V14包含以下所有特权内容</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
@@ -5920,37 +5920,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#300000#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#300000#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>V16 Privilege Pack: #C0xea7004#Orange Probe Set x1</t>
+          <t>V16特权包：#C0xea7004#橙·探测器套装×1</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>#C0xea7004#Unlock Daily Mission: Ally Shards</t>
+          <t>#C0xea7004#日常任务：解放“伙伴碎片”</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#180#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#180#C0x473E37#次</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#110#C0x473E37# times</t>
+          <t>可购买伙伴所持配额容量#C0xea7004#110#C0x473E37#次</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#110#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#110#C0x473E37#次</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Includes all V15 and below perks</t>
+          <t>包含V15以下的所有特权内容</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
@@ -6115,32 +6115,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#500000#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#500000#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>V17 Privilege Pack: #C0xea7004#Orange Gear Chest + Orange Omni-Stone</t>
+          <t>V17特权包：#C0xea7004#橙装备宝箱+橙·万能石</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#210#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#210#C0x473E37#次</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#120#C0x473E37# times</t>
+          <t>可购买伙伴所持配额容量#C0xea7004#120#C0x473E37#次</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#120#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#120#C0x473E37#次</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Includes all V16 and below perks</t>
+          <t>V16包含以下所有特权内容</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
@@ -6297,32 +6297,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Total Top-up: #C0xea7004#800000#C0x473E37# Diamonds for these perks:</t>
+          <t>累计充值#C0xea7004#800000#C0x473E37#钻石可获得以下特权：</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>V18 Privilege Pack: #C0xea7004#Omni-Shard S + Red Rune Choice Box</t>
+          <t>V18特权包：#C0xea7004#万能碎片S+红色符文选定箱</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Daily Growth Support: #C0xea7004#240#C0x473E37# attempts</t>
+          <t>培养支援次数每天#C0xea7004#240#C0x473E37#次</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Buy Ally Slot expansion #C0xea7004#130#C0x473E37# times</t>
+          <t>可购买伙伴所持配额容量#C0xea7004#130#C0x473E37#次</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Daily Probe Exploration: #C0xea7004#130#C0x473E37# attempts</t>
+          <t>探测器每天可探测#C0xea7004#130#C0x473E37#次</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Includes all V17 and below perks</t>
+          <t>V17包含以下所有特权内容</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
